--- a/output/yearly_benthic_cover_iteration_38_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_38_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.59004001247764</v>
+        <v>45.30739797638909</v>
       </c>
       <c r="M2" t="n">
-        <v>98.74144277028685</v>
+        <v>99.88483511953032</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08145679447088</v>
+        <v>87.93283982700198</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92559827211967</v>
+        <v>45.86676213220417</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228871779871343</v>
+        <v>2.228535050845475</v>
       </c>
       <c r="E3" t="n">
-        <v>5.707653167233497</v>
+        <v>5.665887027442763</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429572599571145</v>
+        <v>0.7428450169484919</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97146361061957</v>
+        <v>33.95260252160033</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17603395802726</v>
+        <v>34.17087077963062</v>
       </c>
       <c r="I3" t="n">
-        <v>6.610994144030127</v>
+        <v>6.529318074606235</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643482874731965</v>
+        <v>4.642781355928074</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91854320552912</v>
+        <v>12.067160172998</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91857276356568</v>
+        <v>48.83168809173984</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7627142412145</v>
+        <v>106.765610396942</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.30154364339279</v>
+        <v>86.88231283333243</v>
       </c>
       <c r="C4" t="n">
-        <v>42.78922629771873</v>
+        <v>42.44619235575169</v>
       </c>
       <c r="D4" t="n">
-        <v>2.192003061041448</v>
+        <v>2.177134791862233</v>
       </c>
       <c r="E4" t="n">
-        <v>6.533369563587584</v>
+        <v>6.443952410426325</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744523364249756</v>
+        <v>0.7443989765308018</v>
       </c>
       <c r="G4" t="n">
-        <v>33.40952714060322</v>
+        <v>33.16949948622145</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24807475548877</v>
+        <v>34.24235292041687</v>
       </c>
       <c r="I4" t="n">
-        <v>5.520774731861044</v>
+        <v>5.452480644557251</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653271026560974</v>
+        <v>4.65249360331751</v>
       </c>
       <c r="K4" t="n">
-        <v>12.69845635660721</v>
+        <v>13.11768716666757</v>
       </c>
       <c r="L4" t="n">
-        <v>44.328678619451</v>
+        <v>44.25475053106388</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81636127377693</v>
+        <v>99.81863005348315</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.35640207838357</v>
+        <v>85.52569912671036</v>
       </c>
       <c r="C5" t="n">
-        <v>42.70105583278681</v>
+        <v>41.93566093682948</v>
       </c>
       <c r="D5" t="n">
-        <v>2.146645623104812</v>
+        <v>2.110197198555931</v>
       </c>
       <c r="E5" t="n">
-        <v>7.166317915187251</v>
+        <v>7.004460848385683</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458478681420073</v>
+        <v>0.7457195742466425</v>
       </c>
       <c r="G5" t="n">
-        <v>32.71820942271086</v>
+        <v>32.14967908967028</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30900193453233</v>
+        <v>34.30310041534554</v>
       </c>
       <c r="I5" t="n">
-        <v>4.608830138818767</v>
+        <v>4.551794661464771</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661549175887544</v>
+        <v>4.660747339041515</v>
       </c>
       <c r="K5" t="n">
-        <v>13.64359792161645</v>
+        <v>14.47430087328964</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50199139193394</v>
+        <v>43.43858039419875</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84664514633721</v>
+        <v>99.84854220431787</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.23837058768235</v>
+        <v>83.91258294584959</v>
       </c>
       <c r="C6" t="n">
-        <v>42.29910463550192</v>
+        <v>41.02913423297896</v>
       </c>
       <c r="D6" t="n">
-        <v>2.092687827596585</v>
+        <v>2.030764760243468</v>
       </c>
       <c r="E6" t="n">
-        <v>7.627264471492131</v>
+        <v>7.373945345175445</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469697731595312</v>
+        <v>0.7468449135816851</v>
       </c>
       <c r="G6" t="n">
-        <v>31.89580891355156</v>
+        <v>30.93949484584543</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36060956533842</v>
+        <v>34.3548660247575</v>
       </c>
       <c r="I6" t="n">
-        <v>3.846468954297073</v>
+        <v>3.798886346360534</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668561082247068</v>
+        <v>4.667780709885531</v>
       </c>
       <c r="K6" t="n">
-        <v>14.76162941231763</v>
+        <v>16.08741705415042</v>
       </c>
       <c r="L6" t="n">
-        <v>42.81124289276885</v>
+        <v>42.75700997227436</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8719769405884</v>
+        <v>99.87356125940374</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.88440571943737</v>
+        <v>82.1799586438307</v>
       </c>
       <c r="C7" t="n">
-        <v>41.54299791676272</v>
+        <v>39.88604866648834</v>
       </c>
       <c r="D7" t="n">
-        <v>2.027184518788717</v>
+        <v>1.946050292435637</v>
       </c>
       <c r="E7" t="n">
-        <v>7.923436284630264</v>
+        <v>7.594638641839015</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479224268508523</v>
+        <v>0.7478051459267455</v>
       </c>
       <c r="G7" t="n">
-        <v>30.89743687096141</v>
+        <v>29.64883681817968</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4044316351392</v>
+        <v>34.39903671263027</v>
       </c>
       <c r="I7" t="n">
-        <v>3.209478815249097</v>
+        <v>3.169808870777191</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674515167817826</v>
+        <v>4.673782162042158</v>
       </c>
       <c r="K7" t="n">
-        <v>16.11559428056264</v>
+        <v>17.82004135616929</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23456144283305</v>
+        <v>42.18838535661014</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8931536401584</v>
+        <v>99.89447537926777</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.68184863125107</v>
+        <v>87.00992729100523</v>
       </c>
       <c r="C8" t="n">
-        <v>43.82371643907177</v>
+        <v>42.18561556831746</v>
       </c>
       <c r="D8" t="n">
-        <v>2.03145500577236</v>
+        <v>1.950208739551734</v>
       </c>
       <c r="E8" t="n">
-        <v>9.739777514481807</v>
+        <v>9.422807468659936</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494980076423583</v>
+        <v>0.7494031047074459</v>
       </c>
       <c r="G8" t="n">
-        <v>31.39530538623703</v>
+        <v>30.15334122856926</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47690835154847</v>
+        <v>34.47254281654249</v>
       </c>
       <c r="I8" t="n">
-        <v>5.604541817804312</v>
+        <v>5.57785452855283</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684362547764739</v>
+        <v>4.683769404421535</v>
       </c>
       <c r="K8" t="n">
-        <v>11.31815136874893</v>
+        <v>12.99007270899478</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67170685704311</v>
+        <v>44.63877969533243</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81357466486381</v>
+        <v>99.81446797264466</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.81385765606392</v>
+        <v>84.64614852206094</v>
       </c>
       <c r="C9" t="n">
-        <v>42.82645352475254</v>
+        <v>40.68668379039867</v>
       </c>
       <c r="D9" t="n">
-        <v>1.947037304369954</v>
+        <v>1.84257096304842</v>
       </c>
       <c r="E9" t="n">
-        <v>10.11484523721658</v>
+        <v>9.678857582759857</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508444834431063</v>
+        <v>0.7507773639004003</v>
       </c>
       <c r="G9" t="n">
-        <v>30.09066437375984</v>
+        <v>28.48908932662417</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53884623838288</v>
+        <v>34.53575873941839</v>
       </c>
       <c r="I9" t="n">
-        <v>4.678841997372132</v>
+        <v>4.656736021932216</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692778021519413</v>
+        <v>4.6923585243775</v>
       </c>
       <c r="K9" t="n">
-        <v>13.1861423439361</v>
+        <v>15.35385147793904</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83172241415014</v>
+        <v>43.80452432809138</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84431828283877</v>
+        <v>99.8450595964291</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.73176317418243</v>
+        <v>82.21887591151653</v>
       </c>
       <c r="C10" t="n">
-        <v>41.47113608320972</v>
+        <v>38.98079151772347</v>
       </c>
       <c r="D10" t="n">
-        <v>1.853708163317405</v>
+        <v>1.73351712238633</v>
       </c>
       <c r="E10" t="n">
-        <v>10.28083846824026</v>
+        <v>9.753795729962526</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519979534165899</v>
+        <v>0.751960412433567</v>
       </c>
       <c r="G10" t="n">
-        <v>28.64830071005371</v>
+        <v>26.80294281159734</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59190585716313</v>
+        <v>34.59017897194406</v>
       </c>
       <c r="I10" t="n">
-        <v>3.905024813137663</v>
+        <v>3.886728285482931</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699987208853686</v>
+        <v>4.699752577709792</v>
       </c>
       <c r="K10" t="n">
-        <v>15.26823682581755</v>
+        <v>17.78112408848345</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13065925771241</v>
+        <v>43.10873061540607</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87003216673969</v>
+        <v>99.870646221613</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.50653670108166</v>
+        <v>79.71225510659629</v>
       </c>
       <c r="C11" t="n">
-        <v>39.8519833793074</v>
+        <v>37.07541864444324</v>
       </c>
       <c r="D11" t="n">
-        <v>1.754871812943444</v>
+        <v>1.622231922714441</v>
       </c>
       <c r="E11" t="n">
-        <v>10.27576139838768</v>
+        <v>9.66819469490787</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529879209434899</v>
+        <v>0.7529802715491682</v>
       </c>
       <c r="G11" t="n">
-        <v>27.12082538107301</v>
+        <v>25.08229592322003</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63744436340053</v>
+        <v>34.63709249126171</v>
       </c>
       <c r="I11" t="n">
-        <v>3.258471318436702</v>
+        <v>3.243333105760767</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706174505896811</v>
+        <v>4.7061266971823</v>
       </c>
       <c r="K11" t="n">
-        <v>17.49346329891834</v>
+        <v>20.28774489340372</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5460804102982</v>
+        <v>42.52887178755629</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89152708852394</v>
+        <v>99.89203532540324</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.16037825489138</v>
+        <v>77.23768176174258</v>
       </c>
       <c r="C12" t="n">
-        <v>38.01085352805132</v>
+        <v>35.10159239889347</v>
       </c>
       <c r="D12" t="n">
-        <v>1.651575669483224</v>
+        <v>1.513630922588474</v>
       </c>
       <c r="E12" t="n">
-        <v>10.12398143790234</v>
+        <v>9.471942304006262</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538391183941087</v>
+        <v>0.7538595983149174</v>
       </c>
       <c r="G12" t="n">
-        <v>25.52442577589389</v>
+        <v>23.40315104598249</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67659944612899</v>
+        <v>34.67754152248617</v>
       </c>
       <c r="I12" t="n">
-        <v>2.718462317125665</v>
+        <v>2.705933878896045</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711494489963179</v>
+        <v>4.711622489468232</v>
       </c>
       <c r="K12" t="n">
-        <v>19.83962174510862</v>
+        <v>22.76231823825743</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05901163466125</v>
+        <v>42.04599677657798</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90948690782119</v>
+        <v>99.90990741372886</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.79057879759236</v>
+        <v>74.78953180744908</v>
       </c>
       <c r="C13" t="n">
-        <v>36.06158675508644</v>
+        <v>33.07025806644533</v>
       </c>
       <c r="D13" t="n">
-        <v>1.548148060356668</v>
+        <v>1.407289154339459</v>
       </c>
       <c r="E13" t="n">
-        <v>9.867912380213822</v>
+        <v>9.182683051053179</v>
       </c>
       <c r="F13" t="n">
-        <v>0.75457159585711</v>
+        <v>0.7546180030343893</v>
       </c>
       <c r="G13" t="n">
-        <v>23.92599442266683</v>
+        <v>21.75893750112931</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71029340942705</v>
+        <v>34.71242813958187</v>
       </c>
       <c r="I13" t="n">
-        <v>2.267586454963945</v>
+        <v>2.257213439345935</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716072474106937</v>
+        <v>4.716362518964932</v>
       </c>
       <c r="K13" t="n">
-        <v>22.20942120240764</v>
+        <v>25.21046819255091</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65347920036356</v>
+        <v>41.64410891103444</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92448715785764</v>
+        <v>99.92483517003069</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.24515827917325</v>
+        <v>82.23532437903921</v>
       </c>
       <c r="C14" t="n">
-        <v>40.03611678823578</v>
+        <v>37.83289620798393</v>
       </c>
       <c r="D14" t="n">
-        <v>1.549963955559762</v>
+        <v>1.40885745774177</v>
       </c>
       <c r="E14" t="n">
-        <v>12.09858019353043</v>
+        <v>11.78934644286827</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554566681421164</v>
+        <v>0.7554589602591039</v>
       </c>
       <c r="G14" t="n">
-        <v>25.67907620322411</v>
+        <v>23.92139487423188</v>
       </c>
       <c r="H14" t="n">
-        <v>36.47602459820327</v>
+        <v>36.88932107013719</v>
       </c>
       <c r="I14" t="n">
-        <v>2.96445248462533</v>
+        <v>2.749327072181599</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721604175888228</v>
+        <v>4.721618501619398</v>
       </c>
       <c r="K14" t="n">
-        <v>15.75484172082675</v>
+        <v>17.76467562096082</v>
       </c>
       <c r="L14" t="n">
-        <v>44.11034217715386</v>
+        <v>44.3108859512905</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90130068621639</v>
+        <v>99.90845778023524</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.52503652063119</v>
+        <v>81.50438376079633</v>
       </c>
       <c r="C15" t="n">
-        <v>39.77468477366786</v>
+        <v>37.52596809910559</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5230843965824</v>
+        <v>1.382410268042642</v>
       </c>
       <c r="E15" t="n">
-        <v>12.3009017890713</v>
+        <v>11.95024496312999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562021949289935</v>
+        <v>0.756167494664882</v>
       </c>
       <c r="G15" t="n">
-        <v>25.23374827104038</v>
+        <v>23.47234045454585</v>
       </c>
       <c r="H15" t="n">
-        <v>36.51202117426583</v>
+        <v>36.92391904905985</v>
       </c>
       <c r="I15" t="n">
-        <v>2.47281497643607</v>
+        <v>2.293254689697577</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72626371830621</v>
+        <v>4.726046841655511</v>
       </c>
       <c r="K15" t="n">
-        <v>16.47496347936883</v>
+        <v>18.4956162392037</v>
       </c>
       <c r="L15" t="n">
-        <v>43.66800584461261</v>
+        <v>43.90204546524124</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91765409764929</v>
+        <v>99.92362980355053</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.22503726902991</v>
+        <v>79.13673227489542</v>
       </c>
       <c r="C16" t="n">
-        <v>37.85738392452681</v>
+        <v>35.5120192902738</v>
       </c>
       <c r="D16" t="n">
-        <v>1.43460747417721</v>
+        <v>1.294522369515333</v>
       </c>
       <c r="E16" t="n">
-        <v>11.93007194480266</v>
+        <v>11.50926224905118</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568422311607526</v>
+        <v>0.7567766659295708</v>
       </c>
       <c r="G16" t="n">
-        <v>23.76790409800664</v>
+        <v>21.98006661677374</v>
       </c>
       <c r="H16" t="n">
-        <v>36.54292430652727</v>
+        <v>36.9536650916008</v>
       </c>
       <c r="I16" t="n">
-        <v>2.06242326960068</v>
+        <v>1.912585119964961</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730263944754703</v>
+        <v>4.729854162059816</v>
       </c>
       <c r="K16" t="n">
-        <v>18.77496273097009</v>
+        <v>20.86326772510461</v>
       </c>
       <c r="L16" t="n">
-        <v>43.2989640396021</v>
+        <v>43.56101146546334</v>
       </c>
       <c r="M16" t="n">
-        <v>99.931310695099</v>
+        <v>99.93629848084174</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.82923265272329</v>
+        <v>81.06192970544635</v>
       </c>
       <c r="C17" t="n">
-        <v>39.02811524386026</v>
+        <v>36.91544137079136</v>
       </c>
       <c r="D17" t="n">
-        <v>1.435798736378913</v>
+        <v>1.295518044497232</v>
       </c>
       <c r="E17" t="n">
-        <v>12.68174420906736</v>
+        <v>12.36192086488224</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574706940391795</v>
+        <v>0.7573587366692465</v>
       </c>
       <c r="G17" t="n">
-        <v>24.18550957612358</v>
+        <v>22.52903703974761</v>
       </c>
       <c r="H17" t="n">
-        <v>36.97113784223092</v>
+        <v>37.51415237804606</v>
       </c>
       <c r="I17" t="n">
-        <v>2.063379757138463</v>
+        <v>1.870450537421163</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734191837744871</v>
+        <v>4.733492104182789</v>
       </c>
       <c r="K17" t="n">
-        <v>17.17076734727671</v>
+        <v>18.93807029455365</v>
       </c>
       <c r="L17" t="n">
-        <v>43.73239514887269</v>
+        <v>44.08418790145382</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93127774000966</v>
+        <v>99.93769956679884</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.67016328406666</v>
+        <v>78.81358020056553</v>
       </c>
       <c r="C18" t="n">
-        <v>37.18803436877719</v>
+        <v>34.95526997777955</v>
       </c>
       <c r="D18" t="n">
-        <v>1.355828839951834</v>
+        <v>1.215826029424113</v>
       </c>
       <c r="E18" t="n">
-        <v>12.26219149175526</v>
+        <v>11.86145043329822</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580092591794997</v>
+        <v>0.7578583461934341</v>
       </c>
       <c r="G18" t="n">
-        <v>22.8384456410232</v>
+        <v>21.14319423579717</v>
       </c>
       <c r="H18" t="n">
-        <v>36.99742449093758</v>
+        <v>37.53889947200886</v>
       </c>
       <c r="I18" t="n">
-        <v>1.720705691347406</v>
+        <v>1.559737020134763</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737557869871872</v>
+        <v>4.736614663708961</v>
       </c>
       <c r="K18" t="n">
-        <v>19.32983671593334</v>
+        <v>21.18641979943449</v>
       </c>
       <c r="L18" t="n">
-        <v>43.42481281092451</v>
+        <v>43.80635326341315</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94268389563504</v>
+        <v>99.94804304062718</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.84010541760303</v>
+        <v>78.0206520322765</v>
       </c>
       <c r="C19" t="n">
-        <v>36.62340426702219</v>
+        <v>34.39434638795431</v>
       </c>
       <c r="D19" t="n">
-        <v>1.325752374802994</v>
+        <v>1.188000347206587</v>
       </c>
       <c r="E19" t="n">
-        <v>12.22930832702669</v>
+        <v>11.80797781644734</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584633237094608</v>
+        <v>0.7582818406288382</v>
       </c>
       <c r="G19" t="n">
-        <v>22.33181848121126</v>
+        <v>20.65930608927725</v>
       </c>
       <c r="H19" t="n">
-        <v>37.01958677716009</v>
+        <v>37.55987636712051</v>
       </c>
       <c r="I19" t="n">
-        <v>1.434780360508419</v>
+        <v>1.307948067665744</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740395773184129</v>
+        <v>4.739261503930237</v>
       </c>
       <c r="K19" t="n">
-        <v>20.15989458239698</v>
+        <v>21.97934796772351</v>
       </c>
       <c r="L19" t="n">
-        <v>43.16890377026562</v>
+        <v>43.58273172468979</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95220261968478</v>
+        <v>99.95642608036761</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.43281095940466</v>
+        <v>75.62284125690113</v>
       </c>
       <c r="C20" t="n">
-        <v>34.43732309862262</v>
+        <v>32.19741477202711</v>
       </c>
       <c r="D20" t="n">
-        <v>1.237457734319344</v>
+        <v>1.103890196724804</v>
       </c>
       <c r="E20" t="n">
-        <v>11.61421837715005</v>
+        <v>11.15372248285641</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588539091702559</v>
+        <v>0.7586463211854412</v>
       </c>
       <c r="G20" t="n">
-        <v>20.84452724823294</v>
+        <v>19.19663198475853</v>
       </c>
       <c r="H20" t="n">
-        <v>37.03865073438492</v>
+        <v>37.57793013540392</v>
       </c>
       <c r="I20" t="n">
-        <v>1.196266023833032</v>
+        <v>1.090480628563012</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742836932314098</v>
+        <v>4.741539507409006</v>
       </c>
       <c r="K20" t="n">
-        <v>22.56718904059537</v>
+        <v>24.37715874309887</v>
       </c>
       <c r="L20" t="n">
-        <v>42.9556328507679</v>
+        <v>43.38909459410554</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96014498998588</v>
+        <v>99.96366810923152</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.91230814345663</v>
+        <v>81.52667925115975</v>
       </c>
       <c r="C21" t="n">
-        <v>37.77813697108385</v>
+        <v>35.9571439818581</v>
       </c>
       <c r="D21" t="n">
-        <v>1.238343987761555</v>
+        <v>1.10454523839368</v>
       </c>
       <c r="E21" t="n">
-        <v>13.43371835670401</v>
+        <v>13.15452201785466</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593973918852496</v>
+        <v>0.7590964972571104</v>
       </c>
       <c r="G21" t="n">
-        <v>22.37373351552745</v>
+        <v>20.96031697694572</v>
       </c>
       <c r="H21" t="n">
-        <v>38.57945505249374</v>
+        <v>39.35252247711955</v>
       </c>
       <c r="I21" t="n">
-        <v>1.781426139801812</v>
+        <v>1.451322935732101</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746233699282809</v>
+        <v>4.744353107856939</v>
       </c>
       <c r="K21" t="n">
-        <v>17.08769185654335</v>
+        <v>18.47332074884025</v>
       </c>
       <c r="L21" t="n">
-        <v>45.07483279852831</v>
+        <v>45.52118652795701</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94066162615553</v>
+        <v>99.95165125865535</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_38_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_38_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.30739797638909</v>
+        <v>45.3768109503437</v>
       </c>
       <c r="M2" t="n">
-        <v>99.88483511953032</v>
+        <v>99.77415814160904</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.93283982700198</v>
+        <v>88.04388530982935</v>
       </c>
       <c r="C3" t="n">
-        <v>45.86676213220417</v>
+        <v>45.93342232408406</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228535050845475</v>
+        <v>2.228769537101579</v>
       </c>
       <c r="E3" t="n">
-        <v>5.665887027442763</v>
+        <v>5.709968745468042</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428450169484919</v>
+        <v>0.7429231790338596</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95260252160033</v>
+        <v>33.97459370953825</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17087077963062</v>
+        <v>34.17446623555754</v>
       </c>
       <c r="I3" t="n">
-        <v>6.529318074606235</v>
+        <v>6.569894034168458</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642781355928074</v>
+        <v>4.643269868961623</v>
       </c>
       <c r="K3" t="n">
-        <v>12.067160172998</v>
+        <v>11.95611469017065</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83168809173984</v>
+        <v>48.87464159910835</v>
       </c>
       <c r="M3" t="n">
-        <v>106.765610396942</v>
+        <v>106.7641786133631</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.88231283333243</v>
+        <v>87.22014872164154</v>
       </c>
       <c r="C4" t="n">
-        <v>42.44619235575169</v>
+        <v>42.74500386547729</v>
       </c>
       <c r="D4" t="n">
-        <v>2.177134791862233</v>
+        <v>2.189548142319485</v>
       </c>
       <c r="E4" t="n">
-        <v>6.443952410426325</v>
+        <v>6.52388451981874</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443989765308018</v>
+        <v>0.7444809105533682</v>
       </c>
       <c r="G4" t="n">
-        <v>33.16949948622145</v>
+        <v>33.37671630217923</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24235292041687</v>
+        <v>34.24612188545493</v>
       </c>
       <c r="I4" t="n">
-        <v>5.452480644557251</v>
+        <v>5.486391270357212</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65249360331751</v>
+        <v>4.653005690958551</v>
       </c>
       <c r="K4" t="n">
-        <v>13.11768716666757</v>
+        <v>12.77985127835849</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25475053106388</v>
+        <v>44.29264779965955</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81863005348315</v>
+        <v>99.81750294349533</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.52569912671036</v>
+        <v>86.21677683567403</v>
       </c>
       <c r="C5" t="n">
-        <v>41.93566093682948</v>
+        <v>42.59325677645293</v>
       </c>
       <c r="D5" t="n">
-        <v>2.110197198555931</v>
+        <v>2.141137041484759</v>
       </c>
       <c r="E5" t="n">
-        <v>7.004460848385683</v>
+        <v>7.142988970848694</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457195742466425</v>
+        <v>0.7457992110406425</v>
       </c>
       <c r="G5" t="n">
-        <v>32.14967908967028</v>
+        <v>32.6387541869799</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30310041534554</v>
+        <v>34.30676370786955</v>
       </c>
       <c r="I5" t="n">
-        <v>4.551794661464771</v>
+        <v>4.580088648446456</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660747339041515</v>
+        <v>4.661245069004015</v>
       </c>
       <c r="K5" t="n">
-        <v>14.47430087328964</v>
+        <v>13.78322316432599</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43858039419875</v>
+        <v>43.47112030171116</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84854220431787</v>
+        <v>99.84760024249007</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.91258294584959</v>
+        <v>85.08179773732837</v>
       </c>
       <c r="C6" t="n">
-        <v>41.02913423297896</v>
+        <v>42.1698237354037</v>
       </c>
       <c r="D6" t="n">
-        <v>2.030764760243468</v>
+        <v>2.08628966404269</v>
       </c>
       <c r="E6" t="n">
-        <v>7.373945345175445</v>
+        <v>7.597090185961509</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468449135816851</v>
+        <v>0.7469160911101795</v>
       </c>
       <c r="G6" t="n">
-        <v>30.93949484584543</v>
+        <v>31.80267969223816</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3548660247575</v>
+        <v>34.35814019106825</v>
       </c>
       <c r="I6" t="n">
-        <v>3.798886346360534</v>
+        <v>3.822456343468952</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667780709885531</v>
+        <v>4.668225569438621</v>
       </c>
       <c r="K6" t="n">
-        <v>16.08741705415042</v>
+        <v>14.91820226267163</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75700997227436</v>
+        <v>42.78474931724561</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87356125940374</v>
+        <v>99.87277531532095</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.1799586438307</v>
+        <v>83.62305824021701</v>
       </c>
       <c r="C7" t="n">
-        <v>39.88604866648834</v>
+        <v>41.30513285061185</v>
       </c>
       <c r="D7" t="n">
-        <v>1.946050292435637</v>
+        <v>2.015490355298769</v>
       </c>
       <c r="E7" t="n">
-        <v>7.594638641839015</v>
+        <v>7.870850708743935</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478051459267455</v>
+        <v>0.7478656843035948</v>
       </c>
       <c r="G7" t="n">
-        <v>29.64883681817968</v>
+        <v>30.72343946149678</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39903671263027</v>
+        <v>34.40182147796536</v>
       </c>
       <c r="I7" t="n">
-        <v>3.169808870777191</v>
+        <v>3.189430025511095</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673782162042158</v>
+        <v>4.674160526897467</v>
       </c>
       <c r="K7" t="n">
-        <v>17.82004135616929</v>
+        <v>16.37694175978301</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18838535661014</v>
+        <v>42.21174604673099</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89447537926777</v>
+        <v>99.89382065712586</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.00992729100523</v>
+        <v>88.60246854826687</v>
       </c>
       <c r="C8" t="n">
-        <v>42.18561556831746</v>
+        <v>43.6841958615196</v>
       </c>
       <c r="D8" t="n">
-        <v>1.950208739551734</v>
+        <v>2.019786521909201</v>
       </c>
       <c r="E8" t="n">
-        <v>9.422807468659936</v>
+        <v>9.756738431792773</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494031047074459</v>
+        <v>0.7494598152670825</v>
       </c>
       <c r="G8" t="n">
-        <v>30.15334122856926</v>
+        <v>31.25132718371437</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47254281654249</v>
+        <v>34.47515150228579</v>
       </c>
       <c r="I8" t="n">
-        <v>5.57785452855283</v>
+        <v>5.665881247878387</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683769404421535</v>
+        <v>4.684123845419265</v>
       </c>
       <c r="K8" t="n">
-        <v>12.99007270899478</v>
+        <v>11.39753145173312</v>
       </c>
       <c r="L8" t="n">
-        <v>44.63877969533243</v>
+        <v>44.72981169700908</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81446797264466</v>
+        <v>99.81153901026181</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.64614852206094</v>
+        <v>86.72639891108508</v>
       </c>
       <c r="C9" t="n">
-        <v>40.68668379039867</v>
+        <v>42.68817026659585</v>
       </c>
       <c r="D9" t="n">
-        <v>1.84257096304842</v>
+        <v>1.935233173361386</v>
       </c>
       <c r="E9" t="n">
-        <v>9.678857582759857</v>
+        <v>10.13665541330317</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507773639004003</v>
+        <v>0.7508223602568692</v>
       </c>
       <c r="G9" t="n">
-        <v>28.48908932662417</v>
+        <v>29.94306795369998</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53575873941839</v>
+        <v>34.53782857181598</v>
       </c>
       <c r="I9" t="n">
-        <v>4.656736021932216</v>
+        <v>4.730151687042283</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6923585243775</v>
+        <v>4.692639751605432</v>
       </c>
       <c r="K9" t="n">
-        <v>15.35385147793904</v>
+        <v>13.27360108891492</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80452432809138</v>
+        <v>43.88084305427038</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8450595964291</v>
+        <v>99.84261440978115</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.21887591151653</v>
+        <v>84.57054536913645</v>
       </c>
       <c r="C10" t="n">
-        <v>38.98079151772347</v>
+        <v>41.26689087076197</v>
       </c>
       <c r="D10" t="n">
-        <v>1.73351712238633</v>
+        <v>1.838790151566116</v>
       </c>
       <c r="E10" t="n">
-        <v>9.753795729962526</v>
+        <v>10.28947944218773</v>
       </c>
       <c r="F10" t="n">
-        <v>0.751960412433567</v>
+        <v>0.7519906912577208</v>
       </c>
       <c r="G10" t="n">
-        <v>26.80294281159734</v>
+        <v>28.45084469346101</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59017897194406</v>
+        <v>34.59157179785515</v>
       </c>
       <c r="I10" t="n">
-        <v>3.886728285482931</v>
+        <v>3.947926772447968</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699752577709792</v>
+        <v>4.699941820360754</v>
       </c>
       <c r="K10" t="n">
-        <v>17.78112408848345</v>
+        <v>15.42945463086355</v>
       </c>
       <c r="L10" t="n">
-        <v>43.10873061540607</v>
+        <v>43.17226139595665</v>
       </c>
       <c r="M10" t="n">
-        <v>99.870646221613</v>
+        <v>99.86860689758217</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.71225510659629</v>
+        <v>82.31340957154725</v>
       </c>
       <c r="C11" t="n">
-        <v>37.07541864444324</v>
+        <v>39.62229234372338</v>
       </c>
       <c r="D11" t="n">
-        <v>1.622231922714441</v>
+        <v>1.738827566029375</v>
       </c>
       <c r="E11" t="n">
-        <v>9.66819469490787</v>
+        <v>10.279164686761</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529802715491682</v>
+        <v>0.752993891086543</v>
       </c>
       <c r="G11" t="n">
-        <v>25.08229592322003</v>
+        <v>26.90416466918507</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63709249126171</v>
+        <v>34.63771898998097</v>
       </c>
       <c r="I11" t="n">
-        <v>3.243333105760767</v>
+        <v>3.294327949213395</v>
       </c>
       <c r="J11" t="n">
-        <v>4.7061266971823</v>
+        <v>4.706211819290893</v>
       </c>
       <c r="K11" t="n">
-        <v>20.28774489340372</v>
+        <v>17.68659042845275</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52887178755629</v>
+        <v>42.58145259525588</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89203532540324</v>
+        <v>99.89033536743202</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.23768176174258</v>
+        <v>79.93019967454025</v>
       </c>
       <c r="C12" t="n">
-        <v>35.10159239889347</v>
+        <v>37.74948646455685</v>
       </c>
       <c r="D12" t="n">
-        <v>1.513630922588474</v>
+        <v>1.634229844803311</v>
       </c>
       <c r="E12" t="n">
-        <v>9.471942304006262</v>
+        <v>10.11890008849918</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538595983149174</v>
+        <v>0.7538569538459102</v>
       </c>
       <c r="G12" t="n">
-        <v>23.40315104598249</v>
+        <v>25.28576709436769</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67754152248617</v>
+        <v>34.67741987691186</v>
       </c>
       <c r="I12" t="n">
-        <v>2.705933878896045</v>
+        <v>2.74841985457536</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711622489468232</v>
+        <v>4.711605961536939</v>
       </c>
       <c r="K12" t="n">
-        <v>22.76231823825743</v>
+        <v>20.06980032545974</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04599677657798</v>
+        <v>42.08920410028303</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90990741372886</v>
+        <v>99.90849089029962</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.78953180744908</v>
+        <v>77.39616929400911</v>
       </c>
       <c r="C13" t="n">
-        <v>33.07025806644533</v>
+        <v>35.64044858078709</v>
       </c>
       <c r="D13" t="n">
-        <v>1.407289154339459</v>
+        <v>1.523926610718653</v>
       </c>
       <c r="E13" t="n">
-        <v>9.182683051053179</v>
+        <v>9.81802130398075</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546180030343893</v>
+        <v>0.7546013063663486</v>
       </c>
       <c r="G13" t="n">
-        <v>21.75893750112931</v>
+        <v>23.57909046274868</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71242813958187</v>
+        <v>34.71166009285203</v>
       </c>
       <c r="I13" t="n">
-        <v>2.257213439345935</v>
+        <v>2.292611352552987</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716362518964932</v>
+        <v>4.716258164789678</v>
       </c>
       <c r="K13" t="n">
-        <v>25.21046819255091</v>
+        <v>22.60383070599087</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64410891103444</v>
+        <v>41.6793757172616</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92483517003069</v>
+        <v>99.92365500403957</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.23532437903921</v>
+        <v>84.00619107048252</v>
       </c>
       <c r="C14" t="n">
-        <v>37.83289620798393</v>
+        <v>39.7806733107169</v>
       </c>
       <c r="D14" t="n">
-        <v>1.40885745774177</v>
+        <v>1.525675899710564</v>
       </c>
       <c r="E14" t="n">
-        <v>11.78934644286827</v>
+        <v>12.12523723624566</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554589602591039</v>
+        <v>0.7554675001510254</v>
       </c>
       <c r="G14" t="n">
-        <v>23.92139487423188</v>
+        <v>25.41995622128163</v>
       </c>
       <c r="H14" t="n">
-        <v>36.88932107013719</v>
+        <v>36.56530473546552</v>
       </c>
       <c r="I14" t="n">
-        <v>2.749327072181599</v>
+        <v>2.892877601684211</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721618501619398</v>
+        <v>4.721671875943907</v>
       </c>
       <c r="K14" t="n">
-        <v>17.76467562096082</v>
+        <v>15.99380892951747</v>
       </c>
       <c r="L14" t="n">
-        <v>44.3108859512905</v>
+        <v>44.12919906893501</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90845778023524</v>
+        <v>99.90368130916939</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.50438376079633</v>
+        <v>83.12697709646726</v>
       </c>
       <c r="C15" t="n">
-        <v>37.52596809910559</v>
+        <v>39.32571274091173</v>
       </c>
       <c r="D15" t="n">
-        <v>1.382410268042642</v>
+        <v>1.490066302210041</v>
       </c>
       <c r="E15" t="n">
-        <v>11.95024496312999</v>
+        <v>12.26763012099244</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756167494664882</v>
+        <v>0.7561985068989903</v>
       </c>
       <c r="G15" t="n">
-        <v>23.47234045454585</v>
+        <v>24.84987022388744</v>
       </c>
       <c r="H15" t="n">
-        <v>36.92391904905985</v>
+        <v>36.62390726366671</v>
       </c>
       <c r="I15" t="n">
-        <v>2.293254689697577</v>
+        <v>2.41306401069295</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726046841655511</v>
+        <v>4.726240668118687</v>
       </c>
       <c r="K15" t="n">
-        <v>18.4956162392037</v>
+        <v>16.87302290353274</v>
       </c>
       <c r="L15" t="n">
-        <v>43.90204546524124</v>
+        <v>43.72090664439762</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92362980355053</v>
+        <v>99.91964228884208</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.13673227489542</v>
+        <v>80.51221971340743</v>
       </c>
       <c r="C16" t="n">
-        <v>35.5120192902738</v>
+        <v>37.08415555019199</v>
       </c>
       <c r="D16" t="n">
-        <v>1.294522369515333</v>
+        <v>1.390306733266375</v>
       </c>
       <c r="E16" t="n">
-        <v>11.50926224905118</v>
+        <v>11.78174236581474</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567766659295708</v>
+        <v>0.7568285961554709</v>
       </c>
       <c r="G16" t="n">
-        <v>21.98006661677374</v>
+        <v>23.18617758271823</v>
       </c>
       <c r="H16" t="n">
-        <v>36.9536650916008</v>
+        <v>36.65442349754796</v>
       </c>
       <c r="I16" t="n">
-        <v>1.912585119964961</v>
+        <v>2.012562211932955</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729854162059816</v>
+        <v>4.730178725971692</v>
       </c>
       <c r="K16" t="n">
-        <v>20.86326772510461</v>
+        <v>19.48778028659257</v>
       </c>
       <c r="L16" t="n">
-        <v>43.56101146546334</v>
+        <v>43.36103460736285</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93629848084174</v>
+        <v>99.93297044414741</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.06192970544635</v>
+        <v>82.14303027736293</v>
       </c>
       <c r="C17" t="n">
-        <v>36.91544137079136</v>
+        <v>38.28114370817156</v>
       </c>
       <c r="D17" t="n">
-        <v>1.295518044497232</v>
+        <v>1.391432586094295</v>
       </c>
       <c r="E17" t="n">
-        <v>12.36192086488224</v>
+        <v>12.54109539925999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573587366692465</v>
+        <v>0.7574414663911135</v>
       </c>
       <c r="G17" t="n">
-        <v>22.52903703974761</v>
+        <v>23.62217384296963</v>
       </c>
       <c r="H17" t="n">
-        <v>37.51415237804606</v>
+        <v>37.10132617318779</v>
       </c>
       <c r="I17" t="n">
-        <v>1.870450537421163</v>
+        <v>1.995551644515659</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733492104182789</v>
+        <v>4.734009164944458</v>
       </c>
       <c r="K17" t="n">
-        <v>18.93807029455365</v>
+        <v>17.85696972263706</v>
       </c>
       <c r="L17" t="n">
-        <v>44.08418790145382</v>
+        <v>43.7954220032067</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93769956679884</v>
+        <v>99.93353543401531</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.81358020056553</v>
+        <v>79.64752578793797</v>
       </c>
       <c r="C18" t="n">
-        <v>34.95526997777955</v>
+        <v>36.09379875591723</v>
       </c>
       <c r="D18" t="n">
-        <v>1.215826029424113</v>
+        <v>1.29987676292739</v>
       </c>
       <c r="E18" t="n">
-        <v>11.86145043329822</v>
+        <v>11.99324827568136</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578583461934341</v>
+        <v>0.7579689872274449</v>
       </c>
       <c r="G18" t="n">
-        <v>21.14319423579717</v>
+        <v>22.0678422908708</v>
       </c>
       <c r="H18" t="n">
-        <v>37.53889947200886</v>
+        <v>37.12716542741443</v>
       </c>
       <c r="I18" t="n">
-        <v>1.559737020134763</v>
+        <v>1.664117873644999</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736614663708961</v>
+        <v>4.73730617017153</v>
       </c>
       <c r="K18" t="n">
-        <v>21.18641979943449</v>
+        <v>20.35247421206203</v>
       </c>
       <c r="L18" t="n">
-        <v>43.80635326341315</v>
+        <v>43.4982950418953</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94804304062718</v>
+        <v>99.94456800987457</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.0206520322765</v>
+        <v>78.62103984080863</v>
       </c>
       <c r="C19" t="n">
-        <v>34.39434638795431</v>
+        <v>35.32357785202836</v>
       </c>
       <c r="D19" t="n">
-        <v>1.188000347206587</v>
+        <v>1.262885436385351</v>
       </c>
       <c r="E19" t="n">
-        <v>11.80797781644734</v>
+        <v>11.88321309645661</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582818406288382</v>
+        <v>0.758414899738357</v>
       </c>
       <c r="G19" t="n">
-        <v>20.65930608927725</v>
+        <v>21.43984525027334</v>
       </c>
       <c r="H19" t="n">
-        <v>37.55987636712051</v>
+        <v>37.14900730727728</v>
       </c>
       <c r="I19" t="n">
-        <v>1.307948067665744</v>
+        <v>1.38758072731297</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739261503930237</v>
+        <v>4.74009312336473</v>
       </c>
       <c r="K19" t="n">
-        <v>21.97934796772351</v>
+        <v>21.37896015919137</v>
       </c>
       <c r="L19" t="n">
-        <v>43.58273172468979</v>
+        <v>43.25123649229013</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95642608036761</v>
+        <v>99.95377450350985</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.62284125690113</v>
+        <v>76.02091049854209</v>
       </c>
       <c r="C20" t="n">
-        <v>32.19741477202711</v>
+        <v>32.93694888604723</v>
       </c>
       <c r="D20" t="n">
-        <v>1.103890196724804</v>
+        <v>1.168535707347224</v>
       </c>
       <c r="E20" t="n">
-        <v>11.15372248285641</v>
+        <v>11.1882397113957</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586463211854412</v>
+        <v>0.7587996241982767</v>
       </c>
       <c r="G20" t="n">
-        <v>19.19663198475853</v>
+        <v>19.8380819139469</v>
       </c>
       <c r="H20" t="n">
-        <v>37.57793013540392</v>
+        <v>37.16785204750823</v>
       </c>
       <c r="I20" t="n">
-        <v>1.090480628563012</v>
+        <v>1.156903842906532</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741539507409006</v>
+        <v>4.742497651239228</v>
       </c>
       <c r="K20" t="n">
-        <v>24.37715874309887</v>
+        <v>23.97908950145792</v>
       </c>
       <c r="L20" t="n">
-        <v>43.38909459410554</v>
+        <v>43.04541770340282</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96366810923152</v>
+        <v>99.96145609090797</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.52667925115975</v>
+        <v>82.17355281348797</v>
       </c>
       <c r="C21" t="n">
-        <v>35.9571439818581</v>
+        <v>36.77138124213121</v>
       </c>
       <c r="D21" t="n">
-        <v>1.10454523839368</v>
+        <v>1.169326073941751</v>
       </c>
       <c r="E21" t="n">
-        <v>13.15452201785466</v>
+        <v>13.24491042199504</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7590964972571104</v>
+        <v>0.7593128561612668</v>
       </c>
       <c r="G21" t="n">
-        <v>20.96031697694572</v>
+        <v>21.62270307812407</v>
       </c>
       <c r="H21" t="n">
-        <v>39.35252247711955</v>
+        <v>38.96419460908753</v>
       </c>
       <c r="I21" t="n">
-        <v>1.451322935732101</v>
+        <v>1.66740042317041</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744353107856939</v>
+        <v>4.745705351007915</v>
       </c>
       <c r="K21" t="n">
-        <v>18.47332074884025</v>
+        <v>17.82644718651203</v>
       </c>
       <c r="L21" t="n">
-        <v>45.52118652795701</v>
+        <v>45.34662912469052</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95165125865535</v>
+        <v>99.94445755333375</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_38_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_38_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.3768109503437</v>
+        <v>43.40261646196859</v>
       </c>
       <c r="M2" t="n">
-        <v>99.77415814160904</v>
+        <v>97.09050217763306</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04388530982935</v>
+        <v>81.5325359711796</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93342232408406</v>
+        <v>43.28809152673517</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228769537101579</v>
+        <v>2.183468251933534</v>
       </c>
       <c r="E3" t="n">
-        <v>5.709968745468042</v>
+        <v>4.151386128260678</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429231790338596</v>
+        <v>0.7376722200548935</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97459370953825</v>
+        <v>32.84300162283358</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17446623555754</v>
+        <v>33.9329221225251</v>
       </c>
       <c r="I3" t="n">
-        <v>6.569894034168458</v>
+        <v>3.073634250228723</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643269868961623</v>
+        <v>4.610451375343084</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95611469017065</v>
+        <v>18.4674640288204</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87464159910835</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7641786133631</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.22014872164154</v>
+        <v>88.5254390231451</v>
       </c>
       <c r="C4" t="n">
-        <v>42.74500386547729</v>
+        <v>42.82986226508627</v>
       </c>
       <c r="D4" t="n">
-        <v>2.189548142319485</v>
+        <v>2.189173706989834</v>
       </c>
       <c r="E4" t="n">
-        <v>6.52388451981874</v>
+        <v>6.495731813470058</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444809105533682</v>
+        <v>0.7395997753074496</v>
       </c>
       <c r="G4" t="n">
-        <v>33.37671630217923</v>
+        <v>33.5172724295069</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24612188545493</v>
+        <v>34.02158966414268</v>
       </c>
       <c r="I4" t="n">
-        <v>5.486391270357212</v>
+        <v>6.939573038056619</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653005690958551</v>
+        <v>4.622498595671559</v>
       </c>
       <c r="K4" t="n">
-        <v>12.77985127835849</v>
+        <v>11.47456097685492</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29264779965955</v>
+        <v>45.46486052385909</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81750294349533</v>
+        <v>99.76928376580028</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.21677683567403</v>
+        <v>87.38503206652665</v>
       </c>
       <c r="C5" t="n">
-        <v>42.59325677645293</v>
+        <v>42.76520035727479</v>
       </c>
       <c r="D5" t="n">
-        <v>2.141137041484759</v>
+        <v>2.134725904852042</v>
       </c>
       <c r="E5" t="n">
-        <v>7.142988970848694</v>
+        <v>7.300134344173866</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457992110406425</v>
+        <v>0.741234893142237</v>
       </c>
       <c r="G5" t="n">
-        <v>32.6387541869799</v>
+        <v>32.68365113595061</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30676370786955</v>
+        <v>34.0968050845429</v>
       </c>
       <c r="I5" t="n">
-        <v>4.580088648446456</v>
+        <v>5.795762621726011</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661245069004015</v>
+        <v>4.632718082138981</v>
       </c>
       <c r="K5" t="n">
-        <v>13.78322316432599</v>
+        <v>12.61496793347335</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47112030171116</v>
+        <v>44.42706579152809</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84760024249007</v>
+        <v>99.80723408227622</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.08179773732837</v>
+        <v>85.93676086984323</v>
       </c>
       <c r="C6" t="n">
-        <v>42.1698237354037</v>
+        <v>42.21644211223059</v>
       </c>
       <c r="D6" t="n">
-        <v>2.08628966404269</v>
+        <v>2.06519094375248</v>
       </c>
       <c r="E6" t="n">
-        <v>7.597090185961509</v>
+        <v>7.868823122934619</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469160911101795</v>
+        <v>0.7426261244158184</v>
       </c>
       <c r="G6" t="n">
-        <v>31.80267969223816</v>
+        <v>31.61903838863515</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35814019106825</v>
+        <v>34.16080172312765</v>
       </c>
       <c r="I6" t="n">
-        <v>3.822456343468952</v>
+        <v>4.838867289378641</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668225569438621</v>
+        <v>4.641413277598865</v>
       </c>
       <c r="K6" t="n">
-        <v>14.91820226267163</v>
+        <v>14.06323913015679</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78474931724561</v>
+        <v>43.55932535145355</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87277531532095</v>
+        <v>99.83900659384092</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.62305824021701</v>
+        <v>84.28836821504076</v>
       </c>
       <c r="C7" t="n">
-        <v>41.30513285061185</v>
+        <v>41.31935082623821</v>
       </c>
       <c r="D7" t="n">
-        <v>2.015490355298769</v>
+        <v>1.98643338645582</v>
       </c>
       <c r="E7" t="n">
-        <v>7.870850708743935</v>
+        <v>8.2418781769108</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478656843035948</v>
+        <v>0.7438122670079707</v>
       </c>
       <c r="G7" t="n">
-        <v>30.72343946149678</v>
+        <v>30.41322338392987</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40182147796536</v>
+        <v>34.21536428236665</v>
       </c>
       <c r="I7" t="n">
-        <v>3.189430025511095</v>
+        <v>4.038830049569843</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674160526897467</v>
+        <v>4.648826668799816</v>
       </c>
       <c r="K7" t="n">
-        <v>16.37694175978301</v>
+        <v>15.71163178495923</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21174604673099</v>
+        <v>42.83460440854205</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89382065712586</v>
+        <v>99.86558701973949</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.60246854826687</v>
+        <v>82.37595512231006</v>
       </c>
       <c r="C8" t="n">
-        <v>43.6841958615196</v>
+        <v>40.03388273956956</v>
       </c>
       <c r="D8" t="n">
-        <v>2.019786521909201</v>
+        <v>1.895542091724171</v>
       </c>
       <c r="E8" t="n">
-        <v>9.756738431792773</v>
+        <v>8.426476225796808</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494598152670825</v>
+        <v>0.7448266637139911</v>
       </c>
       <c r="G8" t="n">
-        <v>31.25132718371437</v>
+        <v>29.02163518914006</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47515150228579</v>
+        <v>34.26202653084359</v>
       </c>
       <c r="I8" t="n">
-        <v>5.665881247878387</v>
+        <v>3.370281772878993</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684123845419265</v>
+        <v>4.655166648212444</v>
       </c>
       <c r="K8" t="n">
-        <v>11.39753145173312</v>
+        <v>17.62404487768995</v>
       </c>
       <c r="L8" t="n">
-        <v>44.72981169700908</v>
+        <v>42.22988265914133</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81153901026181</v>
+        <v>99.88781027640084</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.72639891108508</v>
+        <v>80.28687898562201</v>
       </c>
       <c r="C9" t="n">
-        <v>42.68817026659585</v>
+        <v>38.46749872436465</v>
       </c>
       <c r="D9" t="n">
-        <v>1.935233173361386</v>
+        <v>1.796987655943275</v>
       </c>
       <c r="E9" t="n">
-        <v>10.13665541330317</v>
+        <v>8.457001751995614</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508223602568692</v>
+        <v>0.745696186680268</v>
       </c>
       <c r="G9" t="n">
-        <v>29.94306795369998</v>
+        <v>27.51272072398933</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53782857181598</v>
+        <v>34.30202458729233</v>
       </c>
       <c r="I9" t="n">
-        <v>4.730151687042283</v>
+        <v>2.81184691296951</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692639751605432</v>
+        <v>4.660601166751675</v>
       </c>
       <c r="K9" t="n">
-        <v>13.27360108891492</v>
+        <v>19.71312101437797</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88084305427038</v>
+        <v>41.72576132312187</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84261440978115</v>
+        <v>99.90638106186449</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.57054536913645</v>
+        <v>85.30731112039788</v>
       </c>
       <c r="C10" t="n">
-        <v>41.26689087076197</v>
+        <v>41.85028363309696</v>
       </c>
       <c r="D10" t="n">
-        <v>1.838790151566116</v>
+        <v>1.799078437311728</v>
       </c>
       <c r="E10" t="n">
-        <v>10.28947944218773</v>
+        <v>10.38585787039172</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519906912577208</v>
+        <v>0.7465637984796486</v>
       </c>
       <c r="G10" t="n">
-        <v>28.45084469346101</v>
+        <v>28.96747601124739</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59157179785515</v>
+        <v>35.76467917757299</v>
       </c>
       <c r="I10" t="n">
-        <v>3.947926772447968</v>
+        <v>2.977632084896592</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699941820360754</v>
+        <v>4.666023740497804</v>
       </c>
       <c r="K10" t="n">
-        <v>15.42945463086355</v>
+        <v>14.69268887960213</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17226139595665</v>
+        <v>43.3578884320022</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86860689758217</v>
+        <v>99.90086094470129</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.31340957154725</v>
+        <v>84.81184268901859</v>
       </c>
       <c r="C11" t="n">
-        <v>39.62229234372338</v>
+        <v>41.73163028575723</v>
       </c>
       <c r="D11" t="n">
-        <v>1.738827566029375</v>
+        <v>1.772013125510534</v>
       </c>
       <c r="E11" t="n">
-        <v>10.279164686761</v>
+        <v>10.6869270708572</v>
       </c>
       <c r="F11" t="n">
-        <v>0.752993891086543</v>
+        <v>0.7473068835058686</v>
       </c>
       <c r="G11" t="n">
-        <v>26.90416466918507</v>
+        <v>28.56692037879269</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63771898998097</v>
+        <v>35.83550789049813</v>
       </c>
       <c r="I11" t="n">
-        <v>3.294327949213395</v>
+        <v>2.532499317942476</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706211819290893</v>
+        <v>4.670668021911679</v>
       </c>
       <c r="K11" t="n">
-        <v>17.68659042845275</v>
+        <v>15.18815731098141</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58145259525588</v>
+        <v>42.99587969906803</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89033536743202</v>
+        <v>99.91566729580667</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.93019967454025</v>
+        <v>82.66098073116949</v>
       </c>
       <c r="C12" t="n">
-        <v>37.74948646455685</v>
+        <v>39.97404151719807</v>
       </c>
       <c r="D12" t="n">
-        <v>1.634229844803311</v>
+        <v>1.680542025757393</v>
       </c>
       <c r="E12" t="n">
-        <v>10.11890008849918</v>
+        <v>10.48730481913572</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538569538459102</v>
+        <v>0.7479434078549151</v>
       </c>
       <c r="G12" t="n">
-        <v>25.28576709436769</v>
+        <v>27.09229945979936</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67741987691186</v>
+        <v>35.86603105820367</v>
       </c>
       <c r="I12" t="n">
-        <v>2.74841985457536</v>
+        <v>2.112213661325197</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711605961536939</v>
+        <v>4.67464629909322</v>
       </c>
       <c r="K12" t="n">
-        <v>20.06980032545974</v>
+        <v>17.33901926883053</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08920410028303</v>
+        <v>42.61659201069521</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90849089029962</v>
+        <v>99.92965279672381</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.39616929400911</v>
+        <v>83.80065237112142</v>
       </c>
       <c r="C13" t="n">
-        <v>35.64044858078709</v>
+        <v>40.92494105307784</v>
       </c>
       <c r="D13" t="n">
-        <v>1.523926610718653</v>
+        <v>1.681863540849234</v>
       </c>
       <c r="E13" t="n">
-        <v>9.81802130398075</v>
+        <v>11.1190820096869</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546013063663486</v>
+        <v>0.7485315624420508</v>
       </c>
       <c r="G13" t="n">
-        <v>23.57909046274868</v>
+        <v>27.40764577572498</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71166009285203</v>
+        <v>36.18827670692866</v>
       </c>
       <c r="I13" t="n">
-        <v>2.292611352552987</v>
+        <v>1.976930510226774</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716258164789678</v>
+        <v>4.678322265262818</v>
       </c>
       <c r="K13" t="n">
-        <v>22.60383070599087</v>
+        <v>16.19934762887858</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6793757172616</v>
+        <v>42.8098654131144</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92365500403957</v>
+        <v>99.93415409507084</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.00619107048252</v>
+        <v>81.63643864449453</v>
       </c>
       <c r="C14" t="n">
-        <v>39.7806733107169</v>
+        <v>39.06748284405221</v>
       </c>
       <c r="D14" t="n">
-        <v>1.525675899710564</v>
+        <v>1.592408981515471</v>
       </c>
       <c r="E14" t="n">
-        <v>12.12523723624566</v>
+        <v>10.80244141644397</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554675001510254</v>
+        <v>0.7490354193383904</v>
       </c>
       <c r="G14" t="n">
-        <v>25.41995622128163</v>
+        <v>25.9498944090443</v>
       </c>
       <c r="H14" t="n">
-        <v>36.56530473546552</v>
+        <v>36.2126360174779</v>
       </c>
       <c r="I14" t="n">
-        <v>2.892877601684211</v>
+        <v>1.648551029809568</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721671875943907</v>
+        <v>4.68147137086494</v>
       </c>
       <c r="K14" t="n">
-        <v>15.99380892951747</v>
+        <v>18.36356135550546</v>
       </c>
       <c r="L14" t="n">
-        <v>44.12919906893501</v>
+        <v>42.51404106404712</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90368130916939</v>
+        <v>99.9450852636048</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.12697709646726</v>
+        <v>80.64524652733289</v>
       </c>
       <c r="C15" t="n">
-        <v>39.32571274091173</v>
+        <v>38.30121234447991</v>
       </c>
       <c r="D15" t="n">
-        <v>1.490066302210041</v>
+        <v>1.550682107833411</v>
       </c>
       <c r="E15" t="n">
-        <v>12.26763012099244</v>
+        <v>10.75337325867763</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561985068989903</v>
+        <v>0.7494700895847997</v>
       </c>
       <c r="G15" t="n">
-        <v>24.84987022388744</v>
+        <v>25.26991333719774</v>
       </c>
       <c r="H15" t="n">
-        <v>36.62390726366671</v>
+        <v>36.23365045152796</v>
       </c>
       <c r="I15" t="n">
-        <v>2.41306401069295</v>
+        <v>1.403969222606342</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726240668118687</v>
+        <v>4.684188059904998</v>
       </c>
       <c r="K15" t="n">
-        <v>16.87302290353274</v>
+        <v>19.35475347266713</v>
       </c>
       <c r="L15" t="n">
-        <v>43.72090664439762</v>
+        <v>42.29726235077199</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91964228884208</v>
+        <v>99.95322816791902</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.51221971340743</v>
+        <v>78.13933551224291</v>
       </c>
       <c r="C16" t="n">
-        <v>37.08415555019199</v>
+        <v>36.01252350356559</v>
       </c>
       <c r="D16" t="n">
-        <v>1.390306733266375</v>
+        <v>1.447985551429577</v>
       </c>
       <c r="E16" t="n">
-        <v>11.78174236581474</v>
+        <v>10.23630594599637</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568285961554709</v>
+        <v>0.7498443349992333</v>
       </c>
       <c r="G16" t="n">
-        <v>23.18617758271823</v>
+        <v>23.59637040583614</v>
       </c>
       <c r="H16" t="n">
-        <v>36.65442349754796</v>
+        <v>36.25174360523499</v>
       </c>
       <c r="I16" t="n">
-        <v>2.012562211932955</v>
+        <v>1.170558575001375</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730178725971692</v>
+        <v>4.686527093745208</v>
       </c>
       <c r="K16" t="n">
-        <v>19.48778028659257</v>
+        <v>21.86066448775711</v>
       </c>
       <c r="L16" t="n">
-        <v>43.36103460736285</v>
+        <v>42.08781286360491</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93297044414741</v>
+        <v>99.9610008549276</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.14303027736293</v>
+        <v>83.2591694248441</v>
       </c>
       <c r="C17" t="n">
-        <v>38.28114370817156</v>
+        <v>39.37215687198361</v>
       </c>
       <c r="D17" t="n">
-        <v>1.391432586094295</v>
+        <v>1.44876578339035</v>
       </c>
       <c r="E17" t="n">
-        <v>12.54109539925999</v>
+        <v>12.02570564140339</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574414663911135</v>
+        <v>0.7502483808235811</v>
       </c>
       <c r="G17" t="n">
-        <v>23.62217384296963</v>
+        <v>25.16865234377411</v>
       </c>
       <c r="H17" t="n">
-        <v>37.10132617318779</v>
+        <v>37.83084475945307</v>
       </c>
       <c r="I17" t="n">
-        <v>1.995551644515659</v>
+        <v>1.3459001358522</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734009164944458</v>
+        <v>4.689052380147382</v>
       </c>
       <c r="K17" t="n">
-        <v>17.85696972263706</v>
+        <v>16.74083057515591</v>
       </c>
       <c r="L17" t="n">
-        <v>43.7954220032067</v>
+        <v>43.84217337612297</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93353543401531</v>
+        <v>99.95516082326249</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.64752578793797</v>
+        <v>84.88917495568211</v>
       </c>
       <c r="C18" t="n">
-        <v>36.09379875591723</v>
+        <v>40.10923348027848</v>
       </c>
       <c r="D18" t="n">
-        <v>1.29987676292739</v>
+        <v>1.450011084211528</v>
       </c>
       <c r="E18" t="n">
-        <v>11.99324827568136</v>
+        <v>12.63530576200341</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579689872274449</v>
+        <v>0.750893264168728</v>
       </c>
       <c r="G18" t="n">
-        <v>22.0678422908708</v>
+        <v>25.3074996544416</v>
       </c>
       <c r="H18" t="n">
-        <v>37.12716542741443</v>
+        <v>37.86336263265584</v>
       </c>
       <c r="I18" t="n">
-        <v>1.664117873644999</v>
+        <v>2.189019657146445</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73730617017153</v>
+        <v>4.69308290105455</v>
       </c>
       <c r="K18" t="n">
-        <v>20.35247421206203</v>
+        <v>15.11082504431789</v>
       </c>
       <c r="L18" t="n">
-        <v>43.4982950418953</v>
+        <v>44.70703681940996</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94456800987457</v>
+        <v>99.92709534400635</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.62103984080863</v>
+        <v>82.13632494054293</v>
       </c>
       <c r="C19" t="n">
-        <v>35.32357785202836</v>
+        <v>37.69489025762309</v>
       </c>
       <c r="D19" t="n">
-        <v>1.262885436385351</v>
+        <v>1.349680543036446</v>
       </c>
       <c r="E19" t="n">
-        <v>11.88321309645661</v>
+        <v>12.06528746132821</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758414899738357</v>
+        <v>0.7514495675920659</v>
       </c>
       <c r="G19" t="n">
-        <v>21.43984525027334</v>
+        <v>23.55639915337265</v>
       </c>
       <c r="H19" t="n">
-        <v>37.14900730727728</v>
+        <v>37.89141391405194</v>
       </c>
       <c r="I19" t="n">
-        <v>1.38758072731297</v>
+        <v>1.82553450371122</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74009312336473</v>
+        <v>4.696559797450411</v>
       </c>
       <c r="K19" t="n">
-        <v>21.37896015919137</v>
+        <v>17.86367505945707</v>
       </c>
       <c r="L19" t="n">
-        <v>43.25123649229013</v>
+        <v>44.38062858133243</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95377450350985</v>
+        <v>99.9391938984126</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.02091049854209</v>
+        <v>79.29573613307524</v>
       </c>
       <c r="C20" t="n">
-        <v>32.93694888604723</v>
+        <v>35.13577437671042</v>
       </c>
       <c r="D20" t="n">
-        <v>1.168535707347224</v>
+        <v>1.246779025000325</v>
       </c>
       <c r="E20" t="n">
-        <v>11.1882397113957</v>
+        <v>11.39912190246116</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587996241982767</v>
+        <v>0.7519304239548205</v>
       </c>
       <c r="G20" t="n">
-        <v>19.8380819139469</v>
+        <v>21.76042658426866</v>
       </c>
       <c r="H20" t="n">
-        <v>37.16785204750823</v>
+        <v>37.91566082064438</v>
       </c>
       <c r="I20" t="n">
-        <v>1.156903842906532</v>
+        <v>1.522252227028256</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742497651239228</v>
+        <v>4.699565149717627</v>
       </c>
       <c r="K20" t="n">
-        <v>23.97908950145792</v>
+        <v>20.70426386692479</v>
       </c>
       <c r="L20" t="n">
-        <v>43.04541770340282</v>
+        <v>44.10925246459503</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96145609090797</v>
+        <v>99.94929070823024</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.17355281348797</v>
+        <v>76.58660334320615</v>
       </c>
       <c r="C21" t="n">
-        <v>36.77138124213121</v>
+        <v>32.66054906623648</v>
       </c>
       <c r="D21" t="n">
-        <v>1.169326073941751</v>
+        <v>1.149242938272904</v>
       </c>
       <c r="E21" t="n">
-        <v>13.24491042199504</v>
+        <v>10.71890415879933</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593128561612668</v>
+        <v>0.7523458070455804</v>
       </c>
       <c r="G21" t="n">
-        <v>21.62270307812407</v>
+        <v>20.05809857586447</v>
       </c>
       <c r="H21" t="n">
-        <v>38.96419460908753</v>
+        <v>37.93660627500843</v>
       </c>
       <c r="I21" t="n">
-        <v>1.66740042317041</v>
+        <v>1.269244294180554</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745705351007915</v>
+        <v>4.702161294034877</v>
       </c>
       <c r="K21" t="n">
-        <v>17.82644718651203</v>
+        <v>23.41339665679386</v>
       </c>
       <c r="L21" t="n">
-        <v>45.34662912469052</v>
+        <v>43.88376949288556</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94445755333375</v>
+        <v>99.9577152159159</v>
       </c>
     </row>
   </sheetData>
